--- a/data/synth/待影片裁定7句_人工裁定表.xlsx
+++ b/data/synth/待影片裁定7句_人工裁定表.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7句裁定" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="語料庫原始證據" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="詞形一致性22句" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2412,4 +2413,203 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="46" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>合成句採「辭典正式名」，但文化部語料庫（真實聾人用法）偏好另一詞形 —— 兩者皆為同一辭典詞條（正式名／同義索引名），下游可播放性不受影響；問題在於訓練訊號互相矛盾（4,392 句語料教 A、22 句合成教 B）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>合成句採用</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>語料庫偏好</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>語料庫詞頻</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>辭典地位</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>受影響句數</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
+          <t>受影響代碼</t>
+        </is>
+      </c>
+      <c r="G2" s="1" t="inlineStr">
+        <is>
+          <t>例句</t>
+        </is>
+      </c>
+      <c r="H2" s="1" t="inlineStr">
+        <is>
+          <t>【裁定】</t>
+        </is>
+      </c>
+      <c r="I2" s="1" t="inlineStr">
+        <is>
+          <t>【裁定後詞形】</t>
+        </is>
+      </c>
+      <c r="J2" s="1" t="inlineStr">
+        <is>
+          <t>【備註】</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>唸書</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>讀書</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>唸書 7 vs 讀書 61</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>唸書=正式詞條／讀書=同義索引名</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>SYN0891、SYN0892</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>你在哪裡讀書？ → 你/唸書/哪裡</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr"/>
+      <c r="I3" s="2" t="inlineStr"/>
+      <c r="J3" s="2" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>公共汽車</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>公車</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>公共汽車 0 vs 公車 7</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>公共汽車=正式詞條／公車=同義索引名</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>SYN0898、SYN0899、SYN0902、SYN0903、SYN0906、SYN0907、SYN0910、SYN0911、SYN0914、SYN0915</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>我要坐公車去學校。 → 我/公共汽車/坐車/去/學校/要</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>疼</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>痛</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>疼 0 vs 痛 17</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>疼=正式詞條／痛=同義索引名</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>SYN0942、SYN0943、SYN0944、SYN0945、SYN0946、SYN0947、SYN0948、SYN0949、SYN0950、SYN0951</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>我頭痛。 → 我/頭/疼</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>